--- a/data/objetivos.xlsx
+++ b/data/objetivos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Desktop/KELLOGG´S/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Documents/GitHub/JESKELL-TV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41A10315-0E9C-4EB9-AF17-B3B570C40EBC}"/>
+  <xr:revisionPtr revIDLastSave="123" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91D0D2FF-B2B5-41F5-80FE-8676F4566490}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEMANA" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
   <si>
     <t>TABLERO KPI – MAQUILA KELLOGG'S  |  DATOS DE LA SEMANA</t>
   </si>
@@ -225,10 +225,10 @@
     <t>adelanto septiembre</t>
   </si>
   <si>
-    <t>falta stock</t>
-  </si>
-  <si>
     <t>En ejecucion</t>
+  </si>
+  <si>
+    <t>falta totes</t>
   </si>
 </sst>
 </file>
@@ -527,23 +527,23 @@
     <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -856,14 +856,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
+      <c r="A2" s="29"/>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
     </row>
@@ -912,11 +912,11 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
     </row>
     <row r="8" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
@@ -941,11 +941,11 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
     </row>
     <row r="11" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
@@ -959,11 +959,11 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
     </row>
     <row r="13" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
@@ -977,11 +977,11 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
     </row>
     <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
@@ -995,11 +995,11 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
     </row>
     <row r="17" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
@@ -1013,11 +1013,11 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
     </row>
     <row r="19" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
@@ -1053,11 +1053,11 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
     </row>
     <row r="23" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
@@ -1071,11 +1071,11 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
     </row>
     <row r="25" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
@@ -1095,17 +1095,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A18:C18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1124,7 +1124,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>42</v>
       </c>
       <c r="B1" s="25"/>
@@ -1133,7 +1133,7 @@
       <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
+      <c r="A2" s="29"/>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1230,9 +1230,7 @@
         <v>386288</v>
       </c>
       <c r="D8" s="12"/>
-      <c r="E8" s="22" t="s">
-        <v>63</v>
-      </c>
+      <c r="E8" s="22"/>
     </row>
     <row r="9" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
@@ -1259,7 +1257,7 @@
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H10" s="18"/>
     </row>
@@ -1291,7 +1289,7 @@
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1322,7 +1320,7 @@
       <c r="E15" s="16"/>
     </row>
     <row r="17" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="27"/>
+      <c r="A17" s="30"/>
       <c r="B17" s="25"/>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>

--- a/data/objetivos.xlsx
+++ b/data/objetivos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Documents/GitHub/JESKELL-TV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91D0D2FF-B2B5-41F5-80FE-8676F4566490}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6BCD7BE-921B-48FA-BAAB-85F2879B80D3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="66">
   <si>
     <t>TABLERO KPI – MAQUILA KELLOGG'S  |  DATOS DE LA SEMANA</t>
   </si>
@@ -228,7 +228,10 @@
     <t>En ejecucion</t>
   </si>
   <si>
-    <t>falta totes</t>
+    <t>falta de totes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adelanto   </t>
   </si>
 </sst>
 </file>
@@ -238,7 +241,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,13 +325,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF1B8A4C"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <color rgb="FF1B8A4C"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -456,9 +452,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -496,16 +492,16 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -521,10 +517,7 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -856,16 +849,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="29"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
+      <c r="A2" s="28"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -912,11 +905,11 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
     </row>
     <row r="8" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
@@ -941,11 +934,11 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
     </row>
     <row r="11" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
@@ -959,11 +952,11 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
     </row>
     <row r="13" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
@@ -977,11 +970,11 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
     </row>
     <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
@@ -995,11 +988,11 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
     </row>
     <row r="17" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
@@ -1013,11 +1006,11 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
     </row>
     <row r="19" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
@@ -1053,11 +1046,11 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
     </row>
     <row r="23" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
@@ -1071,11 +1064,11 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
     </row>
     <row r="25" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
@@ -1089,9 +1082,9 @@
       </c>
     </row>
     <row r="27" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="28"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
+      <c r="A27" s="27"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1124,20 +1117,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="29"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
+      <c r="A2" s="28"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
     </row>
     <row r="3" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1230,7 +1223,9 @@
         <v>386288</v>
       </c>
       <c r="D8" s="12"/>
-      <c r="E8" s="22"/>
+      <c r="E8" s="22" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
@@ -1243,7 +1238,9 @@
         <v>163940</v>
       </c>
       <c r="D9" s="12"/>
-      <c r="E9" s="23"/>
+      <c r="E9" s="22" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
@@ -1320,11 +1317,11 @@
       <c r="E15" s="16"/>
     </row>
     <row r="17" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="30"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
+      <c r="A17" s="29"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/data/objetivos.xlsx
+++ b/data/objetivos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Documents/GitHub/JESKELL-TV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="128" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6BCD7BE-921B-48FA-BAAB-85F2879B80D3}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEDB84FB-6C58-4A93-8840-DD82576C3B02}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -916,7 +916,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="6">
-        <v>72000</v>
+        <v>86016</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>14</v>
@@ -927,7 +927,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="6">
-        <v>72000</v>
+        <v>22632</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>16</v>
@@ -1281,8 +1281,7 @@
         <v>205178</v>
       </c>
       <c r="C12" s="11">
-        <f>73120+3904+19584</f>
-        <v>96608</v>
+        <v>119240</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="22" t="s">

--- a/data/objetivos.xlsx
+++ b/data/objetivos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Documents/GitHub/JESKELL-TV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEDB84FB-6C58-4A93-8840-DD82576C3B02}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88C310FF-02A3-4620-96EB-F35BAABBA85F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="65">
   <si>
     <t>TABLERO KPI – MAQUILA KELLOGG'S  |  DATOS DE LA SEMANA</t>
   </si>
@@ -51,18 +51,12 @@
     <t>SEMANA</t>
   </si>
   <si>
-    <t>31/08 al 06/09/2026</t>
-  </si>
-  <si>
     <t>Rango de fechas de la semana (texto libre)</t>
   </si>
   <si>
     <t>PERIODO</t>
   </si>
   <si>
-    <t>AGOSTO 2026</t>
-  </si>
-  <si>
     <t>Mes y año del período</t>
   </si>
   <si>
@@ -232,6 +226,9 @@
   </si>
   <si>
     <t xml:space="preserve">Adelanto   </t>
+  </si>
+  <si>
+    <t>07/09 al 13/09/2026</t>
   </si>
 </sst>
 </file>
@@ -454,7 +451,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -536,6 +533,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -876,209 +876,209 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="30">
+        <v>46266</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" s="5">
         <v>0.85</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="25" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="26"/>
     </row>
     <row r="8" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B8" s="6">
         <v>86016</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B9" s="6">
         <v>22632</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B10" s="26"/>
       <c r="C10" s="26"/>
     </row>
     <row r="11" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B11" s="7">
         <v>75</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="25" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B12" s="26"/>
       <c r="C12" s="26"/>
     </row>
     <row r="13" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B13" s="7">
         <v>88</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B14" s="26"/>
       <c r="C14" s="26"/>
     </row>
     <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15" s="7">
         <v>83</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16" s="26"/>
       <c r="C16" s="26"/>
     </row>
     <row r="17" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17" s="7">
         <v>80</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="26"/>
     </row>
     <row r="19" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B19" s="6">
         <v>3408000</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B20" s="6">
         <v>3600000</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B21" s="8">
         <v>0.94699999999999995</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="26"/>
     </row>
     <row r="23" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B23" s="17">
         <v>46023</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="26"/>
     </row>
     <row r="25" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -1118,7 +1118,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -1134,27 +1134,27 @@
     </row>
     <row r="3" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="F3" s="20" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B4" s="10">
         <v>344376</v>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B5" s="10">
         <v>592364</v>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B6" s="10">
         <v>394880</v>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B7" s="10">
         <v>282102</v>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B8" s="21">
         <v>374682</v>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B9" s="21">
         <v>152802</v>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B10" s="21">
         <v>174824</v>
@@ -1254,13 +1254,13 @@
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B11" s="10">
         <v>407060</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B12" s="21">
         <v>205178</v>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="22" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="14"/>
@@ -1299,7 +1299,7 @@
     </row>
     <row r="14" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="14"/>
@@ -1308,7 +1308,7 @@
     </row>
     <row r="15" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="14"/>

--- a/data/objetivos.xlsx
+++ b/data/objetivos.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="134" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88C310FF-02A3-4620-96EB-F35BAABBA85F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEMANA" sheetId="1" r:id="rId1"/>
